--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
+    <t xml:space="preserve">Colchane</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Colchane</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:21</t>
+    <t xml:space="preserve">2026-09-09 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -581,7 +581,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -594,7 +594,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:17</t>
+    <t xml:space="preserve">2026-09-17 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
+    <t xml:space="preserve">Camiña</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:12</t>
+    <t xml:space="preserve">2026-09-23 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -581,9 +581,11 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1403</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>1402</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
@@ -594,9 +596,11 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>1403</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:41</t>
+    <t xml:space="preserve">2026-10-02 14:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:55</t>
+    <t xml:space="preserve">2026-10-05 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
